--- a/output/files/PH_Bosa_resultados.xlsx
+++ b/output/files/PH_Bosa_resultados.xlsx
@@ -7015,7 +7015,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Territoriales 2023: match exacto (sin tildes/mayúsculas) por corporación: 'PACTO HISTÓRICO' en Concejo y JAL, 'PACTO HISTÓRICO BOGOTÁ' en Alcaldía (la coalición de Bolívar se registró con ese nombre distinto). Otras variantes como 'PACTO HISTORICO COLOMBIA PUEDE' o 'COALICIÓN PACTO POR USME' siguen excluidas.</t>
+          <t>Territoriales 2023: se cuenta como PH cualquier partido cuyo nombre contenga 'PACTO' (sin tildes) -- cubre 'PACTO HISTÓRICO', 'PACTO HISTÓRICO BOGOTÁ' (Alcaldía), 'PACTO HISTÓRICO COLOMBIA PUEDE', 'COALICIÓN PACTO HISTÓRICO' y 'COALICIÓN PACTO POR USME' (variantes por corporación/localidad, todas confirmadas como parte de la coalición de PH).</t>
         </is>
       </c>
     </row>
